--- a/Demo/ONCHO/epi/demo_oncho_epi_9999_1_site.xlsx
+++ b/Demo/ONCHO/epi/demo_oncho_epi_9999_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\epi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E0D70F-EF1E-4BE2-9014-0E1CE8895B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7120D581-7DBF-419C-A77F-002C62818C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="201">
   <si>
     <t>type</t>
   </si>
@@ -456,9 +456,6 @@
     <t>DEMO (Month YYYY) 1. ONCHO Stop - Site Form</t>
   </si>
   <si>
-    <t>iso2_oncho_stop_1_site_yyyymm</t>
-  </si>
-  <si>
     <t>Estimated number of eligible children (5–9 years) living in this village</t>
   </si>
   <si>
@@ -640,6 +637,12 @@
   </si>
   <si>
     <t>if(${c_site_1} != 'Other' and ${c_health_facility} != 'Other', concat(${c_site_id_1}), concat(${c_site_id_2}))</t>
+  </si>
+  <si>
+    <t>demo_oncho_epi_9999_1_site</t>
+  </si>
+  <si>
+    <t>${c_admin1}</t>
   </si>
 </sst>
 </file>
@@ -1295,10 +1298,10 @@
     </row>
     <row r="5" spans="1:17" s="6" customFormat="1" ht="36">
       <c r="A5" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>133</v>
@@ -1322,7 +1325,7 @@
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
     </row>
-    <row r="6" spans="1:17" s="6" customFormat="1">
+    <row r="6" spans="1:17" s="6" customFormat="1" ht="36">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
@@ -1344,22 +1347,26 @@
       <c r="K6" s="18"/>
       <c r="L6" s="17"/>
       <c r="M6" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+        <v>142</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>77</v>
+      </c>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1">
       <c r="A7" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="17"/>
@@ -1373,7 +1380,7 @@
       <c r="K7" s="18"/>
       <c r="L7" s="17"/>
       <c r="M7" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
@@ -1385,17 +1392,17 @@
         <v>34</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" s="18"/>
       <c r="H8" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="18" t="s">
@@ -1411,20 +1418,20 @@
     </row>
     <row r="9" spans="1:17" s="6" customFormat="1" ht="31.5">
       <c r="A9" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>178</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>179</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
       <c r="G9" s="18"/>
       <c r="H9" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18" t="s">
@@ -1433,7 +1440,7 @@
       <c r="K9" s="18"/>
       <c r="L9" s="17"/>
       <c r="M9" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
@@ -1445,17 +1452,17 @@
         <v>34</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="18"/>
       <c r="F10" s="17"/>
       <c r="G10" s="18"/>
       <c r="H10" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="18" t="s">
@@ -1471,20 +1478,20 @@
     </row>
     <row r="11" spans="1:17" s="6" customFormat="1" ht="31.5">
       <c r="A11" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>181</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>182</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="18"/>
       <c r="F11" s="17"/>
       <c r="G11" s="18"/>
       <c r="H11" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18" t="s">
@@ -1493,7 +1500,7 @@
       <c r="K11" s="18"/>
       <c r="L11" s="17"/>
       <c r="M11" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
@@ -1502,20 +1509,20 @@
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" ht="31.5">
       <c r="A12" s="26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="27"/>
       <c r="F12" s="26"/>
       <c r="G12" s="27"/>
       <c r="H12" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I12" s="27"/>
       <c r="J12" s="27" t="s">
@@ -1524,7 +1531,7 @@
       <c r="K12" s="27"/>
       <c r="L12" s="29"/>
       <c r="M12" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -1536,10 +1543,10 @@
         <v>34</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="18"/>
@@ -1547,7 +1554,7 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
@@ -1569,10 +1576,10 @@
         <v>34</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="18"/>
@@ -1580,7 +1587,7 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J14" s="18"/>
       <c r="K14" s="18"/>
@@ -1591,7 +1598,7 @@
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q14" s="21" t="s">
         <v>77</v>
@@ -1624,7 +1631,7 @@
         <v>82</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="18"/>
@@ -1678,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="23"/>
@@ -1794,7 +1801,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" s="24"/>
       <c r="E22" s="23"/>
@@ -1821,7 +1828,7 @@
         <v>84</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="23"/>
@@ -1829,7 +1836,7 @@
         <v>86</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="23"/>
@@ -1852,7 +1859,7 @@
         <v>85</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="23"/>
@@ -1876,10 +1883,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="23"/>
@@ -1900,13 +1907,13 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B26" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>161</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>162</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="23"/>
@@ -1956,24 +1963,24 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B28" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>169</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="23"/>
       <c r="F28" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G28" s="23" t="s">
-        <v>174</v>
-      </c>
       <c r="H28" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="18" t="s">
@@ -1989,21 +1996,21 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B29" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>170</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>171</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>175</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>176</v>
       </c>
       <c r="H29" s="23"/>
       <c r="I29" s="23"/>
@@ -2146,16 +2153,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2518,26 +2525,26 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E31" s="26"/>
       <c r="F31" s="31"/>
@@ -2558,7 +2565,7 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>92</v>
@@ -2599,7 +2606,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>94</v>
@@ -2614,7 +2621,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>93</v>
@@ -2629,7 +2636,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>95</v>
@@ -2644,7 +2651,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>96</v>
@@ -2659,7 +2666,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>97</v>
@@ -2674,7 +2681,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>98</v>
@@ -2689,7 +2696,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>99</v>
@@ -2711,7 +2718,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>100</v>
@@ -2725,7 +2732,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>101</v>
@@ -2739,7 +2746,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>102</v>
@@ -2753,7 +2760,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>103</v>
@@ -2767,7 +2774,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>104</v>
@@ -2781,7 +2788,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>105</v>
@@ -2795,7 +2802,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>106</v>
@@ -2809,7 +2816,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>107</v>
@@ -2823,7 +2830,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>108</v>
@@ -2837,7 +2844,7 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>109</v>
@@ -2851,7 +2858,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>110</v>
@@ -2865,7 +2872,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>111</v>
@@ -2879,7 +2886,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>112</v>
@@ -2893,7 +2900,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>113</v>
@@ -2907,7 +2914,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>114</v>
@@ -2921,7 +2928,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>115</v>
@@ -2935,7 +2942,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>116</v>
@@ -2949,7 +2956,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>117</v>
@@ -2963,7 +2970,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>118</v>
@@ -2977,7 +2984,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>119</v>
@@ -2991,7 +2998,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>120</v>
@@ -3005,7 +3012,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>121</v>
@@ -3019,7 +3026,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>122</v>
@@ -3033,7 +3040,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>123</v>
@@ -3047,7 +3054,7 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>124</v>
@@ -3061,7 +3068,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>125</v>
@@ -3075,7 +3082,7 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>126</v>
@@ -3089,7 +3096,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>127</v>
@@ -3103,7 +3110,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>99</v>
@@ -3117,7 +3124,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>99</v>
@@ -3131,7 +3138,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>99</v>
@@ -3145,7 +3152,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>99</v>
@@ -3159,7 +3166,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>99</v>
@@ -3173,7 +3180,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>99</v>
@@ -3187,7 +3194,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B81" s="5">
         <v>113</v>
@@ -3201,7 +3208,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B82" s="5">
         <v>124</v>
@@ -3215,7 +3222,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" s="5">
         <v>125</v>
@@ -3229,7 +3236,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B84" s="5">
         <v>103</v>
@@ -3243,7 +3250,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B85" s="5">
         <v>114</v>
@@ -3257,7 +3264,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B86" s="5">
         <v>126</v>
@@ -3271,7 +3278,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B87" s="5">
         <v>107</v>
@@ -3285,7 +3292,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B88" s="5">
         <v>115</v>
@@ -3299,7 +3306,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B89" s="5">
         <v>101</v>
@@ -3313,7 +3320,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B90" s="5">
         <v>104</v>
@@ -3327,7 +3334,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B91" s="5">
         <v>116</v>
@@ -3341,7 +3348,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B92" s="5">
         <v>105</v>
@@ -3355,7 +3362,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B93" s="5">
         <v>108</v>
@@ -3369,7 +3376,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B94" s="5">
         <v>109</v>
@@ -3383,7 +3390,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B95" s="5">
         <v>110</v>
@@ -3397,7 +3404,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B96" s="5">
         <v>106</v>
@@ -3411,7 +3418,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B97" s="5">
         <v>117</v>
@@ -3425,7 +3432,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B98" s="5">
         <v>118</v>
@@ -3439,7 +3446,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B99" s="5">
         <v>123</v>
@@ -3453,7 +3460,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B100" s="5">
         <v>119</v>
@@ -3467,7 +3474,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B101" s="5">
         <v>120</v>
@@ -3481,7 +3488,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B102" s="5">
         <v>127</v>
@@ -3495,7 +3502,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B103" s="5">
         <v>128</v>
@@ -3509,7 +3516,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B104" s="5">
         <v>111</v>
@@ -3523,7 +3530,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B105" s="5">
         <v>102</v>
@@ -3537,7 +3544,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B106" s="5">
         <v>112</v>
@@ -3551,7 +3558,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B107" s="5">
         <v>121</v>
@@ -3565,7 +3572,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B108" s="5">
         <v>122</v>
@@ -3579,7 +3586,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B110" s="5">
         <v>113</v>
@@ -3597,7 +3604,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B111" s="5">
         <v>124</v>
@@ -3615,7 +3622,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B112" s="5">
         <v>125</v>
@@ -3633,7 +3640,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B113" s="5">
         <v>103</v>
@@ -3651,7 +3658,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B114" s="5">
         <v>114</v>
@@ -3669,7 +3676,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B115" s="5">
         <v>126</v>
@@ -3687,7 +3694,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B116" s="5">
         <v>107</v>
@@ -3705,7 +3712,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B117" s="5">
         <v>115</v>
@@ -3723,7 +3730,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B118" s="5">
         <v>101</v>
@@ -3741,7 +3748,7 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B119" s="5">
         <v>104</v>
@@ -3759,7 +3766,7 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B120" s="5">
         <v>116</v>
@@ -3777,7 +3784,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B121" s="5">
         <v>105</v>
@@ -3795,7 +3802,7 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B122" s="5">
         <v>108</v>
@@ -3813,7 +3820,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B123" s="5">
         <v>109</v>
@@ -3831,7 +3838,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B124" s="5">
         <v>110</v>
@@ -3849,7 +3856,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B125" s="5">
         <v>106</v>
@@ -3867,7 +3874,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B126" s="5">
         <v>117</v>
@@ -3885,7 +3892,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B127" s="5">
         <v>118</v>
@@ -3903,7 +3910,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B128" s="5">
         <v>123</v>
@@ -3921,7 +3928,7 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B129" s="5">
         <v>119</v>
@@ -3939,7 +3946,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B130" s="5">
         <v>120</v>
@@ -3957,7 +3964,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B131" s="5">
         <v>127</v>
@@ -3975,7 +3982,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B132" s="5">
         <v>128</v>
@@ -3993,7 +4000,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B133" s="5">
         <v>111</v>
@@ -4011,7 +4018,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B134" s="5">
         <v>102</v>
@@ -4029,7 +4036,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B135" s="5">
         <v>112</v>
@@ -4047,7 +4054,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B136" s="5">
         <v>121</v>
@@ -4065,7 +4072,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B137" s="5">
         <v>122</v>
@@ -4120,7 +4127,7 @@
         <v>137</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>

--- a/Demo/ONCHO/epi/demo_oncho_epi_9999_1_site.xlsx
+++ b/Demo/ONCHO/epi/demo_oncho_epi_9999_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\ONCHO\epi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7120D581-7DBF-419C-A77F-002C62818C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A11E05B-1D5B-4C5E-BF5D-02EEF60B4037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="202">
   <si>
     <t>type</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t>${c_admin1}</t>
+  </si>
+  <si>
+    <t>${c_gps_type} = 'Manual Entry'</t>
   </si>
 </sst>
 </file>
@@ -1948,7 +1951,9 @@
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="H27" s="23" t="s">
+        <v>166</v>
+      </c>
       <c r="I27" s="23"/>
       <c r="J27" s="18" t="s">
         <v>15</v>
@@ -1980,7 +1985,7 @@
         <v>173</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="18" t="s">
@@ -2012,7 +2017,9 @@
       <c r="G29" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="H29" s="23"/>
+      <c r="H29" s="23" t="s">
+        <v>201</v>
+      </c>
       <c r="I29" s="23"/>
       <c r="J29" s="18" t="s">
         <v>15</v>
